--- a/welfare_results.xlsx
+++ b/welfare_results.xlsx
@@ -91,11 +91,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -501,19 +502,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0008557945868405883</v>
+        <v>0.000856041519337076</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001707493452947777</v>
+        <v>0.001708095469549189</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002613116624001399</v>
+        <v>0.002614583285184368</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003396949682265706</v>
+        <v>0.003398733875479911</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0038468124252422</v>
+        <v>0.003847394530182561</v>
       </c>
     </row>
   </sheetData>
@@ -763,7 +764,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
+      <c r="A3" s="2" t="n"/>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
@@ -807,7 +808,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
@@ -851,7 +852,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
@@ -895,7 +896,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n"/>
+      <c r="A9" s="2" t="n"/>
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
@@ -939,7 +940,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="2" t="n"/>
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
@@ -983,7 +984,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
+      <c r="A13" s="2" t="n"/>
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
@@ -1027,7 +1028,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n"/>
+      <c r="A15" s="2" t="n"/>
       <c r="B15" s="1" t="n">
         <v>1</v>
       </c>
@@ -1071,7 +1072,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n"/>
+      <c r="A17" s="2" t="n"/>
       <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
@@ -1115,7 +1116,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n"/>
+      <c r="A19" s="2" t="n"/>
       <c r="B19" s="1" t="n">
         <v>1</v>
       </c>
@@ -1159,7 +1160,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n"/>
+      <c r="A21" s="2" t="n"/>
       <c r="B21" s="1" t="n">
         <v>1</v>
       </c>
@@ -1203,7 +1204,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n"/>
+      <c r="A23" s="2" t="n"/>
       <c r="B23" s="1" t="n">
         <v>1</v>
       </c>
@@ -1247,7 +1248,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n"/>
+      <c r="A25" s="2" t="n"/>
       <c r="B25" s="1" t="n">
         <v>1</v>
       </c>
@@ -1291,7 +1292,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n"/>
+      <c r="A27" s="2" t="n"/>
       <c r="B27" s="1" t="n">
         <v>1</v>
       </c>
@@ -1335,7 +1336,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n"/>
+      <c r="A29" s="2" t="n"/>
       <c r="B29" s="1" t="n">
         <v>1</v>
       </c>
@@ -1379,7 +1380,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n"/>
+      <c r="A31" s="2" t="n"/>
       <c r="B31" s="1" t="n">
         <v>1</v>
       </c>
@@ -1423,7 +1424,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n"/>
+      <c r="A33" s="2" t="n"/>
       <c r="B33" s="1" t="n">
         <v>1</v>
       </c>
@@ -1467,7 +1468,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n"/>
+      <c r="A35" s="2" t="n"/>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
@@ -1511,7 +1512,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n"/>
+      <c r="A37" s="2" t="n"/>
       <c r="B37" s="1" t="n">
         <v>1</v>
       </c>
@@ -1555,7 +1556,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n"/>
+      <c r="A39" s="2" t="n"/>
       <c r="B39" s="1" t="n">
         <v>1</v>
       </c>
@@ -1599,7 +1600,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n"/>
+      <c r="A41" s="2" t="n"/>
       <c r="B41" s="1" t="n">
         <v>1</v>
       </c>
@@ -1643,7 +1644,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n"/>
+      <c r="A43" s="2" t="n"/>
       <c r="B43" s="1" t="n">
         <v>1</v>
       </c>
@@ -1687,7 +1688,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n"/>
+      <c r="A45" s="2" t="n"/>
       <c r="B45" s="1" t="n">
         <v>1</v>
       </c>
@@ -1731,7 +1732,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n"/>
+      <c r="A47" s="2" t="n"/>
       <c r="B47" s="1" t="n">
         <v>1</v>
       </c>
@@ -1775,7 +1776,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n"/>
+      <c r="A49" s="2" t="n"/>
       <c r="B49" s="1" t="n">
         <v>1</v>
       </c>
@@ -1819,7 +1820,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n"/>
+      <c r="A51" s="2" t="n"/>
       <c r="B51" s="1" t="n">
         <v>1</v>
       </c>
@@ -1863,7 +1864,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n"/>
+      <c r="A53" s="2" t="n"/>
       <c r="B53" s="1" t="n">
         <v>1</v>
       </c>
@@ -1907,7 +1908,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n"/>
+      <c r="A55" s="2" t="n"/>
       <c r="B55" s="1" t="n">
         <v>1</v>
       </c>
@@ -1951,7 +1952,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n"/>
+      <c r="A57" s="2" t="n"/>
       <c r="B57" s="1" t="n">
         <v>1</v>
       </c>
@@ -1995,7 +1996,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n"/>
+      <c r="A59" s="2" t="n"/>
       <c r="B59" s="1" t="n">
         <v>1</v>
       </c>
@@ -2039,7 +2040,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n"/>
+      <c r="A61" s="2" t="n"/>
       <c r="B61" s="1" t="n">
         <v>1</v>
       </c>
@@ -2083,7 +2084,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n"/>
+      <c r="A63" s="2" t="n"/>
       <c r="B63" s="1" t="n">
         <v>1</v>
       </c>
@@ -2127,7 +2128,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n"/>
+      <c r="A65" s="2" t="n"/>
       <c r="B65" s="1" t="n">
         <v>1</v>
       </c>
@@ -2171,7 +2172,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n"/>
+      <c r="A67" s="2" t="n"/>
       <c r="B67" s="1" t="n">
         <v>1</v>
       </c>
@@ -2215,7 +2216,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n"/>
+      <c r="A69" s="2" t="n"/>
       <c r="B69" s="1" t="n">
         <v>1</v>
       </c>
@@ -2259,7 +2260,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n"/>
+      <c r="A71" s="2" t="n"/>
       <c r="B71" s="1" t="n">
         <v>1</v>
       </c>
@@ -2303,7 +2304,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n"/>
+      <c r="A73" s="2" t="n"/>
       <c r="B73" s="1" t="n">
         <v>1</v>
       </c>
@@ -2347,7 +2348,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n"/>
+      <c r="A75" s="2" t="n"/>
       <c r="B75" s="1" t="n">
         <v>1</v>
       </c>
@@ -2391,7 +2392,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n"/>
+      <c r="A77" s="2" t="n"/>
       <c r="B77" s="1" t="n">
         <v>1</v>
       </c>
@@ -2435,7 +2436,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n"/>
+      <c r="A79" s="2" t="n"/>
       <c r="B79" s="1" t="n">
         <v>1</v>
       </c>
@@ -2479,7 +2480,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n"/>
+      <c r="A81" s="2" t="n"/>
       <c r="B81" s="1" t="n">
         <v>1</v>
       </c>
@@ -2523,7 +2524,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n"/>
+      <c r="A83" s="2" t="n"/>
       <c r="B83" s="1" t="n">
         <v>1</v>
       </c>
@@ -2567,7 +2568,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n"/>
+      <c r="A85" s="2" t="n"/>
       <c r="B85" s="1" t="n">
         <v>1</v>
       </c>
@@ -2611,7 +2612,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n"/>
+      <c r="A87" s="2" t="n"/>
       <c r="B87" s="1" t="n">
         <v>1</v>
       </c>
@@ -2655,7 +2656,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n"/>
+      <c r="A89" s="2" t="n"/>
       <c r="B89" s="1" t="n">
         <v>1</v>
       </c>
@@ -2699,7 +2700,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n"/>
+      <c r="A91" s="2" t="n"/>
       <c r="B91" s="1" t="n">
         <v>1</v>
       </c>
@@ -2743,7 +2744,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n"/>
+      <c r="A93" s="2" t="n"/>
       <c r="B93" s="1" t="n">
         <v>1</v>
       </c>
@@ -2787,7 +2788,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n"/>
+      <c r="A95" s="2" t="n"/>
       <c r="B95" s="1" t="n">
         <v>1</v>
       </c>
@@ -2831,7 +2832,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n"/>
+      <c r="A97" s="2" t="n"/>
       <c r="B97" s="1" t="n">
         <v>1</v>
       </c>
@@ -2875,7 +2876,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n"/>
+      <c r="A99" s="2" t="n"/>
       <c r="B99" s="1" t="n">
         <v>1</v>
       </c>
@@ -2919,7 +2920,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n"/>
+      <c r="A101" s="2" t="n"/>
       <c r="B101" s="1" t="n">
         <v>1</v>
       </c>
@@ -2963,7 +2964,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n"/>
+      <c r="A103" s="2" t="n"/>
       <c r="B103" s="1" t="n">
         <v>1</v>
       </c>
@@ -3007,7 +3008,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n"/>
+      <c r="A105" s="2" t="n"/>
       <c r="B105" s="1" t="n">
         <v>1</v>
       </c>
@@ -3051,7 +3052,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n"/>
+      <c r="A107" s="2" t="n"/>
       <c r="B107" s="1" t="n">
         <v>1</v>
       </c>
@@ -3095,7 +3096,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n"/>
+      <c r="A109" s="2" t="n"/>
       <c r="B109" s="1" t="n">
         <v>1</v>
       </c>
@@ -3139,7 +3140,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n"/>
+      <c r="A111" s="2" t="n"/>
       <c r="B111" s="1" t="n">
         <v>1</v>
       </c>
@@ -3183,7 +3184,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n"/>
+      <c r="A113" s="2" t="n"/>
       <c r="B113" s="1" t="n">
         <v>1</v>
       </c>
@@ -3227,7 +3228,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n"/>
+      <c r="A115" s="2" t="n"/>
       <c r="B115" s="1" t="n">
         <v>1</v>
       </c>
@@ -3271,7 +3272,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n"/>
+      <c r="A117" s="2" t="n"/>
       <c r="B117" s="1" t="n">
         <v>1</v>
       </c>
@@ -3684,7 +3685,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
+      <c r="A3" s="2" t="n"/>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
@@ -3728,7 +3729,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
@@ -3772,7 +3773,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
@@ -3816,7 +3817,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n"/>
+      <c r="A9" s="2" t="n"/>
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
@@ -3860,7 +3861,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="2" t="n"/>
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
@@ -3904,7 +3905,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
+      <c r="A13" s="2" t="n"/>
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
@@ -3948,7 +3949,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n"/>
+      <c r="A15" s="2" t="n"/>
       <c r="B15" s="1" t="n">
         <v>1</v>
       </c>
@@ -3992,7 +3993,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n"/>
+      <c r="A17" s="2" t="n"/>
       <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
@@ -4036,7 +4037,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n"/>
+      <c r="A19" s="2" t="n"/>
       <c r="B19" s="1" t="n">
         <v>1</v>
       </c>
@@ -4080,7 +4081,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n"/>
+      <c r="A21" s="2" t="n"/>
       <c r="B21" s="1" t="n">
         <v>1</v>
       </c>
@@ -4124,7 +4125,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n"/>
+      <c r="A23" s="2" t="n"/>
       <c r="B23" s="1" t="n">
         <v>1</v>
       </c>
@@ -4168,7 +4169,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n"/>
+      <c r="A25" s="2" t="n"/>
       <c r="B25" s="1" t="n">
         <v>1</v>
       </c>
@@ -4212,7 +4213,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n"/>
+      <c r="A27" s="2" t="n"/>
       <c r="B27" s="1" t="n">
         <v>1</v>
       </c>
@@ -4256,7 +4257,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n"/>
+      <c r="A29" s="2" t="n"/>
       <c r="B29" s="1" t="n">
         <v>1</v>
       </c>
@@ -4300,7 +4301,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n"/>
+      <c r="A31" s="2" t="n"/>
       <c r="B31" s="1" t="n">
         <v>1</v>
       </c>
@@ -4344,7 +4345,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n"/>
+      <c r="A33" s="2" t="n"/>
       <c r="B33" s="1" t="n">
         <v>1</v>
       </c>
@@ -4388,7 +4389,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n"/>
+      <c r="A35" s="2" t="n"/>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
@@ -4432,7 +4433,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n"/>
+      <c r="A37" s="2" t="n"/>
       <c r="B37" s="1" t="n">
         <v>1</v>
       </c>
@@ -4476,7 +4477,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n"/>
+      <c r="A39" s="2" t="n"/>
       <c r="B39" s="1" t="n">
         <v>1</v>
       </c>
@@ -4520,7 +4521,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n"/>
+      <c r="A41" s="2" t="n"/>
       <c r="B41" s="1" t="n">
         <v>1</v>
       </c>
@@ -4564,7 +4565,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n"/>
+      <c r="A43" s="2" t="n"/>
       <c r="B43" s="1" t="n">
         <v>1</v>
       </c>
@@ -4608,7 +4609,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n"/>
+      <c r="A45" s="2" t="n"/>
       <c r="B45" s="1" t="n">
         <v>1</v>
       </c>
@@ -4652,7 +4653,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n"/>
+      <c r="A47" s="2" t="n"/>
       <c r="B47" s="1" t="n">
         <v>1</v>
       </c>
@@ -4696,7 +4697,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n"/>
+      <c r="A49" s="2" t="n"/>
       <c r="B49" s="1" t="n">
         <v>1</v>
       </c>
@@ -4740,7 +4741,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n"/>
+      <c r="A51" s="2" t="n"/>
       <c r="B51" s="1" t="n">
         <v>1</v>
       </c>
@@ -4784,7 +4785,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n"/>
+      <c r="A53" s="2" t="n"/>
       <c r="B53" s="1" t="n">
         <v>1</v>
       </c>
@@ -4828,7 +4829,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n"/>
+      <c r="A55" s="2" t="n"/>
       <c r="B55" s="1" t="n">
         <v>1</v>
       </c>
@@ -4872,7 +4873,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n"/>
+      <c r="A57" s="2" t="n"/>
       <c r="B57" s="1" t="n">
         <v>1</v>
       </c>
@@ -4916,7 +4917,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n"/>
+      <c r="A59" s="2" t="n"/>
       <c r="B59" s="1" t="n">
         <v>1</v>
       </c>
@@ -4960,7 +4961,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n"/>
+      <c r="A61" s="2" t="n"/>
       <c r="B61" s="1" t="n">
         <v>1</v>
       </c>
@@ -5004,7 +5005,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n"/>
+      <c r="A63" s="2" t="n"/>
       <c r="B63" s="1" t="n">
         <v>1</v>
       </c>
@@ -5048,7 +5049,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n"/>
+      <c r="A65" s="2" t="n"/>
       <c r="B65" s="1" t="n">
         <v>1</v>
       </c>
@@ -5092,7 +5093,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n"/>
+      <c r="A67" s="2" t="n"/>
       <c r="B67" s="1" t="n">
         <v>1</v>
       </c>
@@ -5136,7 +5137,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n"/>
+      <c r="A69" s="2" t="n"/>
       <c r="B69" s="1" t="n">
         <v>1</v>
       </c>
@@ -5180,7 +5181,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n"/>
+      <c r="A71" s="2" t="n"/>
       <c r="B71" s="1" t="n">
         <v>1</v>
       </c>
@@ -5224,7 +5225,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n"/>
+      <c r="A73" s="2" t="n"/>
       <c r="B73" s="1" t="n">
         <v>1</v>
       </c>
@@ -5268,7 +5269,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n"/>
+      <c r="A75" s="2" t="n"/>
       <c r="B75" s="1" t="n">
         <v>1</v>
       </c>
@@ -5312,7 +5313,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n"/>
+      <c r="A77" s="2" t="n"/>
       <c r="B77" s="1" t="n">
         <v>1</v>
       </c>
@@ -5356,7 +5357,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n"/>
+      <c r="A79" s="2" t="n"/>
       <c r="B79" s="1" t="n">
         <v>1</v>
       </c>
@@ -5400,7 +5401,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n"/>
+      <c r="A81" s="2" t="n"/>
       <c r="B81" s="1" t="n">
         <v>1</v>
       </c>
@@ -5444,7 +5445,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n"/>
+      <c r="A83" s="2" t="n"/>
       <c r="B83" s="1" t="n">
         <v>1</v>
       </c>
@@ -5488,7 +5489,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n"/>
+      <c r="A85" s="2" t="n"/>
       <c r="B85" s="1" t="n">
         <v>1</v>
       </c>
@@ -5532,7 +5533,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n"/>
+      <c r="A87" s="2" t="n"/>
       <c r="B87" s="1" t="n">
         <v>1</v>
       </c>
@@ -5576,7 +5577,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n"/>
+      <c r="A89" s="2" t="n"/>
       <c r="B89" s="1" t="n">
         <v>1</v>
       </c>
@@ -5620,7 +5621,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n"/>
+      <c r="A91" s="2" t="n"/>
       <c r="B91" s="1" t="n">
         <v>1</v>
       </c>
@@ -5664,7 +5665,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n"/>
+      <c r="A93" s="2" t="n"/>
       <c r="B93" s="1" t="n">
         <v>1</v>
       </c>
@@ -5708,7 +5709,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n"/>
+      <c r="A95" s="2" t="n"/>
       <c r="B95" s="1" t="n">
         <v>1</v>
       </c>
@@ -5752,7 +5753,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n"/>
+      <c r="A97" s="2" t="n"/>
       <c r="B97" s="1" t="n">
         <v>1</v>
       </c>
@@ -5796,7 +5797,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n"/>
+      <c r="A99" s="2" t="n"/>
       <c r="B99" s="1" t="n">
         <v>1</v>
       </c>
@@ -5840,7 +5841,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n"/>
+      <c r="A101" s="2" t="n"/>
       <c r="B101" s="1" t="n">
         <v>1</v>
       </c>
@@ -5884,7 +5885,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n"/>
+      <c r="A103" s="2" t="n"/>
       <c r="B103" s="1" t="n">
         <v>1</v>
       </c>
@@ -5928,7 +5929,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n"/>
+      <c r="A105" s="2" t="n"/>
       <c r="B105" s="1" t="n">
         <v>1</v>
       </c>
@@ -5972,7 +5973,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n"/>
+      <c r="A107" s="2" t="n"/>
       <c r="B107" s="1" t="n">
         <v>1</v>
       </c>
@@ -6016,7 +6017,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n"/>
+      <c r="A109" s="2" t="n"/>
       <c r="B109" s="1" t="n">
         <v>1</v>
       </c>
@@ -6060,7 +6061,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n"/>
+      <c r="A111" s="2" t="n"/>
       <c r="B111" s="1" t="n">
         <v>1</v>
       </c>
@@ -6104,7 +6105,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n"/>
+      <c r="A113" s="2" t="n"/>
       <c r="B113" s="1" t="n">
         <v>1</v>
       </c>
@@ -6148,7 +6149,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n"/>
+      <c r="A115" s="2" t="n"/>
       <c r="B115" s="1" t="n">
         <v>1</v>
       </c>
@@ -6192,7 +6193,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n"/>
+      <c r="A117" s="2" t="n"/>
       <c r="B117" s="1" t="n">
         <v>1</v>
       </c>
@@ -6323,19 +6324,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.002337434147453855</v>
+        <v>-0.002337142822877912</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.001964108870992277</v>
+        <v>-0.001963517962032874</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00167632923473012</v>
+        <v>-0.001675767799911089</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.001283614453517856</v>
+        <v>-0.001283253308203782</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0008537046621094695</v>
+        <v>-0.0008537301876228084</v>
       </c>
     </row>
   </sheetData>
@@ -6389,19 +6390,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006398252219367382</v>
+        <v>0.0006433111427229105</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005792851489541352</v>
+        <v>0.0006002329842291626</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005765071440938995</v>
+        <v>0.0006019384319796107</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0006401644230126808</v>
+        <v>0.0006463539761405067</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0006761731698064046</v>
+        <v>0.000684270345628543</v>
       </c>
     </row>
   </sheetData>
@@ -6463,19 +6464,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04053642829123102</v>
+        <v>0.0005452654064601447</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03880297293101449</v>
+        <v>0.0004904736951229982</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03247671915407319</v>
+        <v>0.0005190544444315572</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02410388252149677</v>
+        <v>0.0006189015258806652</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0177911128058943</v>
+        <v>0.0006028219511745947</v>
       </c>
     </row>
     <row r="3">
@@ -6486,19 +6487,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04051958310135143</v>
+        <v>0.0005213620810844291</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03879059780334509</v>
+        <v>0.0004702624409654247</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03247007922966375</v>
+        <v>0.000504339413921708</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02410790065369268</v>
+        <v>0.0006174897079247949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01779560423313566</v>
+        <v>0.0006032709217577616</v>
       </c>
     </row>
     <row r="4">
@@ -6509,19 +6510,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04050860135051497</v>
+        <v>0.0005032471765531905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03878421471625674</v>
+        <v>0.0004560845643988044</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03247012425294334</v>
+        <v>0.0004962304866927818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02411940359501273</v>
+        <v>0.0006232383803938301</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01780833906053616</v>
+        <v>0.000611704786435685</v>
       </c>
     </row>
     <row r="5">
@@ -6532,19 +6533,19 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04050544402749219</v>
+        <v>0.0004925091299034868</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03878517573511211</v>
+        <v>0.0004491206311477902</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03248079612356929</v>
+        <v>0.0004995905412141224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02414119850918132</v>
+        <v>0.0006394072016422166</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01783176905613859</v>
+        <v>0.0006309663418085478</v>
       </c>
     </row>
     <row r="6">
@@ -6555,19 +6556,19 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04050834696600079</v>
+        <v>0.0004879515248200966</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03879221339685864</v>
+        <v>0.00044808252968282</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03249794829064562</v>
+        <v>0.0005092714746805886</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0241710912834067</v>
+        <v>0.0006636865910260867</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01786141923868503</v>
+        <v>0.0006566741119560793</v>
       </c>
     </row>
     <row r="7">
@@ -6578,19 +6579,19 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04051713010677031</v>
+        <v>0.0004894990788403396</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03880536105523055</v>
+        <v>0.0004531909440040373</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03252222786925783</v>
+        <v>0.0005262203924178699</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02420687578912566</v>
+        <v>0.0006929192114071775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01789703717689436</v>
+        <v>0.0006879196222753367</v>
       </c>
     </row>
     <row r="8">
@@ -6601,19 +6602,19 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04053165421589316</v>
+        <v>0.0004967825072277688</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03882415618316916</v>
+        <v>0.000463993913070674</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03255343447008145</v>
+        <v>0.0005503608319046647</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02424801035860467</v>
+        <v>0.0007264986686103024</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01793920571823447</v>
+        <v>0.0007266431557983741</v>
       </c>
     </row>
     <row r="9">
@@ -6624,19 +6625,19 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04055626233589651</v>
+        <v>0.0005135439837683376</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03885338048982021</v>
+        <v>0.000484684571615916</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03259425417241289</v>
+        <v>0.0005832043979474609</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02430295136649812</v>
+        <v>0.0007746027471481854</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01799682354496418</v>
+        <v>0.0007813828038624356</v>
       </c>
     </row>
     <row r="10">
@@ -6647,19 +6648,19 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04058847088297197</v>
+        <v>0.0005382087728018096</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0388902582193942</v>
+        <v>0.0005134084948171663</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03264403255966664</v>
+        <v>0.0006255606881358138</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02436829851748142</v>
+        <v>0.0008336551711169348</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01806363855893951</v>
+        <v>0.0008466623600697082</v>
       </c>
     </row>
     <row r="11">
@@ -6670,19 +6671,19 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04062685553602206</v>
+        <v>0.0005694855316888342</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03893330066623363</v>
+        <v>0.0005490156879971331</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03270217474870777</v>
+        <v>0.0006777856326860097</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02444177192849642</v>
+        <v>0.0009012957232954946</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0181418660319568</v>
+        <v>0.0009247254958108537</v>
       </c>
     </row>
     <row r="12">
@@ -6693,19 +6694,19 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04067925044829875</v>
+        <v>0.0006144814293440439</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03899159618362191</v>
+        <v>0.0006005136560667543</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03277136231768017</v>
+        <v>0.0007398415571724069</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02452958876951279</v>
+        <v>0.0009833751417413572</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01823540594224282</v>
+        <v>0.001018610703193196</v>
       </c>
     </row>
     <row r="13">
@@ -6716,19 +6717,19 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04074764417996536</v>
+        <v>0.0006743211202516275</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03906757997087582</v>
+        <v>0.0006687872197902846</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03285493192288175</v>
+        <v>0.0008148498162981839</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02463320296409358</v>
+        <v>0.001080497847808347</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01834126703835926</v>
+        <v>0.001124416863126697</v>
       </c>
     </row>
     <row r="14">
@@ -6739,19 +6740,19 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04082696162057524</v>
+        <v>0.0007449749551850298</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0391527033043124</v>
+        <v>0.0007467158174256309</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0329503311197937</v>
+        <v>0.0009017561030263679</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02474855175897082</v>
+        <v>0.001190426164144631</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01846580294686092</v>
+        <v>0.001249838441836944</v>
       </c>
     </row>
     <row r="15">
@@ -6762,19 +6763,19 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04092786548930522</v>
+        <v>0.0008373599906297303</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0392557845830767</v>
+        <v>0.0008414963858548842</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03306569460511449</v>
+        <v>0.00100915535427779</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02488248391321012</v>
+        <v>0.001319052062884166</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0186080666311848</v>
+        <v>0.001393339554899049</v>
       </c>
     </row>
     <row r="16">
@@ -6785,19 +6786,19 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04105135966167043</v>
+        <v>0.0009517460875725281</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03937928006205341</v>
+        <v>0.0009549872021090786</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03320072634038079</v>
+        <v>0.00113606504478621</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02503537518073849</v>
+        <v>0.001467141111815803</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01876566430750948</v>
+        <v>0.001552929526983883</v>
       </c>
     </row>
     <row r="17">
@@ -6808,19 +6809,19 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04118351720974615</v>
+        <v>0.001076890681840824</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03951431120263228</v>
+        <v>0.001082998423302706</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03334922737292641</v>
+        <v>0.001278721098256419</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02520207116761309</v>
+        <v>0.001632176779242774</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0189449677087733</v>
+        <v>0.001736423414410021</v>
       </c>
     </row>
     <row r="18">
@@ -6831,19 +6832,19 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04135124389503637</v>
+        <v>0.001236749489760676</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03968367071168107</v>
+        <v>0.001246965385422852</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03352897450840922</v>
+        <v>0.001452419159314804</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02539210954031104</v>
+        <v>0.001819570497044477</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01914462757930208</v>
+        <v>0.001941607209725931</v>
       </c>
     </row>
     <row r="19">
@@ -6854,19 +6855,19 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04155240229477971</v>
+        <v>0.001428414959990373</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03988441635943805</v>
+        <v>0.001440734726499437</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03373020059578218</v>
+        <v>0.001647648932040718</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02560792974762996</v>
+        <v>0.002031778284834103</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01936730482356428</v>
+        <v>0.00216987208123311</v>
       </c>
     </row>
     <row r="20">
@@ -6877,19 +6878,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04175832775907459</v>
+        <v>0.001628568328131269</v>
       </c>
       <c r="D20" t="n">
-        <v>0.04009130985692042</v>
+        <v>0.001644999908786767</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03393947693717804</v>
+        <v>0.001855386918996161</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0258280351864494</v>
+        <v>0.002249183982725905</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0196043212836108</v>
+        <v>0.002413030509148875</v>
       </c>
     </row>
     <row r="21">
@@ -6900,19 +6901,19 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04199279298661315</v>
+        <v>0.001857654542974592</v>
       </c>
       <c r="D21" t="n">
-        <v>0.04032066911332302</v>
+        <v>0.001872182764201033</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03417103667646298</v>
+        <v>0.002085646307500813</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02606379682583145</v>
+        <v>0.002484013494310922</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0198524678353244</v>
+        <v>0.002666420023593741</v>
       </c>
     </row>
     <row r="22">
@@ -6923,19 +6924,19 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04224608453673263</v>
+        <v>0.002104897090505607</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04056151508330439</v>
+        <v>0.002111343178590534</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03441640934337219</v>
+        <v>0.002329469366097574</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02631371715305966</v>
+        <v>0.002733520792133619</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02011064775120258</v>
+        <v>0.002930107311871636</v>
       </c>
     </row>
     <row r="23">
@@ -6946,19 +6947,19 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04250734018052698</v>
+        <v>0.002362949666246503</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0408147224916443</v>
+        <v>0.002363745283944994</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03467081362067407</v>
+        <v>0.002584930320713163</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02657655251449091</v>
+        <v>0.00299748295281041</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02038521193992619</v>
+        <v>0.003210919063515867</v>
       </c>
     </row>
     <row r="24">
@@ -6969,19 +6970,19 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04278276720970056</v>
+        <v>0.002636886513139996</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04108775957952488</v>
+        <v>0.002637194388481198</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03494321984155949</v>
+        <v>0.002861003786219736</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02685081747921066</v>
+        <v>0.003276183677924947</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02067278236637853</v>
+        <v>0.003503229417279811</v>
       </c>
     </row>
     <row r="25">
@@ -6992,19 +6993,19 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0430808001602007</v>
+        <v>0.002934399773490151</v>
       </c>
       <c r="D25" t="n">
-        <v>0.04138098503468039</v>
+        <v>0.002931173068870955</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03522905132840976</v>
+        <v>0.003151378421361001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0271343447736519</v>
+        <v>0.003562131194341733</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02096933602948197</v>
+        <v>0.003803749195304578</v>
       </c>
     </row>
     <row r="26">
@@ -7015,19 +7016,19 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0433898481749217</v>
+        <v>0.003242655866426338</v>
       </c>
       <c r="D26" t="n">
-        <v>0.04168092372269255</v>
+        <v>0.003232184234001349</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03551758344183938</v>
+        <v>0.003446900324837224</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02742077736974303</v>
+        <v>0.00385206546871512</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0212701555535106</v>
+        <v>0.004107531782205619</v>
       </c>
     </row>
     <row r="27">
@@ -7038,19 +7039,19 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.04370087360987428</v>
+        <v>0.003553058113950735</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04198203048558073</v>
+        <v>0.003534827562209801</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03580803337587077</v>
+        <v>0.003743062240609628</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02770895525891366</v>
+        <v>0.004145310321726833</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02157376970233606</v>
+        <v>0.004414616625313728</v>
       </c>
     </row>
     <row r="28">
@@ -7061,19 +7062,19 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.04401383144703596</v>
+        <v>0.003866818472188986</v>
       </c>
       <c r="D28" t="n">
-        <v>0.04228289053422969</v>
+        <v>0.00383948184476591</v>
       </c>
       <c r="E28" t="n">
-        <v>0.03609768274214725</v>
+        <v>0.004040264572811716</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02799691072145884</v>
+        <v>0.004439979008980244</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02187751752656307</v>
+        <v>0.004722972941906317</v>
       </c>
     </row>
     <row r="29">
@@ -7084,19 +7085,19 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.04435209509978642</v>
+        <v>0.004201251836432003</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04260502824147581</v>
+        <v>0.004163757077668809</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03640616959970803</v>
+        <v>0.004352855152811359</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0282929416305036</v>
+        <v>0.004737828474912087</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02218197793564653</v>
+        <v>0.005030223442040542</v>
       </c>
     </row>
     <row r="30">
@@ -7107,19 +7108,19 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04466527985575072</v>
+        <v>0.004512720033494219</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04289126049866036</v>
+        <v>0.004459827750568231</v>
       </c>
       <c r="E30" t="n">
-        <v>0.036690326315389</v>
+        <v>0.004644551381927931</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02857067263671523</v>
+        <v>0.005020414665759768</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02246867566329132</v>
+        <v>0.005322168826557911</v>
       </c>
     </row>
     <row r="31">
@@ -7130,19 +7131,19 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.004824057763470779</v>
+        <v>0.004823519991143098</v>
       </c>
       <c r="D31" t="n">
-        <v>0.004756970749370892</v>
+        <v>0.00475645902751968</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004937572038613858</v>
+        <v>0.004937150146979432</v>
       </c>
       <c r="F31" t="n">
-        <v>0.005305120906336178</v>
+        <v>0.005304812701233419</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0056149303387221</v>
+        <v>0.005614705028013444</v>
       </c>
     </row>
     <row r="32">
@@ -7153,19 +7154,19 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.005179132577297641</v>
+        <v>0.005088483477808998</v>
       </c>
       <c r="D32" t="n">
-        <v>0.005096509178548864</v>
+        <v>0.005010285055493198</v>
       </c>
       <c r="E32" t="n">
-        <v>0.005266340404578537</v>
+        <v>0.005195311108606711</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00561180239011885</v>
+        <v>0.005559916946871949</v>
       </c>
       <c r="G32" t="n">
-        <v>0.005920540874305918</v>
+        <v>0.005882867304574781</v>
       </c>
     </row>
     <row r="33">
@@ -7176,19 +7177,19 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.005482555944945603</v>
+        <v>0.005392123587500046</v>
       </c>
       <c r="D33" t="n">
-        <v>0.005385682900034191</v>
+        <v>0.005299677547208378</v>
       </c>
       <c r="E33" t="n">
-        <v>0.005547562272068351</v>
+        <v>0.005476709291260939</v>
       </c>
       <c r="F33" t="n">
-        <v>0.005886141250462336</v>
+        <v>0.005834386000462795</v>
       </c>
       <c r="G33" t="n">
-        <v>0.006197451893122129</v>
+        <v>0.0061598699111289</v>
       </c>
     </row>
     <row r="34">
@@ -7199,19 +7200,19 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005780993523701787</v>
+        <v>0.005690831909093899</v>
       </c>
       <c r="D34" t="n">
-        <v>0.005669352004768873</v>
+        <v>0.005583614957460915</v>
       </c>
       <c r="E34" t="n">
-        <v>0.005822604065870813</v>
+        <v>0.005751971528372396</v>
       </c>
       <c r="F34" t="n">
-        <v>0.006159155308953362</v>
+        <v>0.006107565290287149</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00646304539709574</v>
+        <v>0.006425574216248666</v>
       </c>
     </row>
     <row r="35">
@@ -7222,19 +7223,19 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.006086852109333957</v>
+        <v>0.005996781754858403</v>
       </c>
       <c r="D35" t="n">
-        <v>0.005961216711627037</v>
+        <v>0.005875576454160069</v>
       </c>
       <c r="E35" t="n">
-        <v>0.006104520929533626</v>
+        <v>0.006033971277489312</v>
       </c>
       <c r="F35" t="n">
-        <v>0.006431579754991796</v>
+        <v>0.006380041662897296</v>
       </c>
       <c r="G35" t="n">
-        <v>0.006727084193679666</v>
+        <v>0.006689640031369421</v>
       </c>
     </row>
     <row r="36">
@@ -7245,19 +7246,19 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.006379453324009483</v>
+        <v>0.006289336418388408</v>
       </c>
       <c r="D36" t="n">
-        <v>0.006238877673390136</v>
+        <v>0.006153201910209656</v>
       </c>
       <c r="E36" t="n">
-        <v>0.006373519503632645</v>
+        <v>0.006302944715802238</v>
       </c>
       <c r="F36" t="n">
-        <v>0.006687529819215979</v>
+        <v>0.006635962128905663</v>
       </c>
       <c r="G36" t="n">
-        <v>0.006979807481618793</v>
+        <v>0.006942338120290787</v>
       </c>
     </row>
     <row r="37">
@@ -7268,19 +7269,19 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00665584596193418</v>
+        <v>0.00656570756348793</v>
       </c>
       <c r="D37" t="n">
-        <v>0.006500749744891987</v>
+        <v>0.006415061616475358</v>
       </c>
       <c r="E37" t="n">
-        <v>0.006633279923459392</v>
+        <v>0.006562700455536934</v>
       </c>
       <c r="F37" t="n">
-        <v>0.006939278738395514</v>
+        <v>0.006887695438473682</v>
       </c>
       <c r="G37" t="n">
-        <v>0.007230585703017926</v>
+        <v>0.007193101098164119</v>
       </c>
     </row>
     <row r="38">
@@ -7291,19 +7292,19 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.006934030397005088</v>
+        <v>0.006844010335390839</v>
       </c>
       <c r="D38" t="n">
-        <v>0.006769371550167514</v>
+        <v>0.006683802215603817</v>
       </c>
       <c r="E38" t="n">
-        <v>0.006895486469625465</v>
+        <v>0.006825006610388413</v>
       </c>
       <c r="F38" t="n">
-        <v>0.007192188675135847</v>
+        <v>0.007140669068278038</v>
       </c>
       <c r="G38" t="n">
-        <v>0.007476056483792819</v>
+        <v>0.007438611269325241</v>
       </c>
     </row>
     <row r="39">
@@ -7314,19 +7315,19 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.007229077950335157</v>
+        <v>0.007139842341453956</v>
       </c>
       <c r="D39" t="n">
-        <v>0.007054763996386161</v>
+        <v>0.006969944826060358</v>
       </c>
       <c r="E39" t="n">
-        <v>0.007169984668912516</v>
+        <v>0.007100124342425508</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00745489385288299</v>
+        <v>0.007403820264996619</v>
       </c>
       <c r="G39" t="n">
-        <v>0.007723994460112785</v>
+        <v>0.007686865045073561</v>
       </c>
     </row>
     <row r="40">
@@ -7337,19 +7338,19 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.007501711908491786</v>
+        <v>0.007412896798207973</v>
       </c>
       <c r="D40" t="n">
-        <v>0.007320176651041116</v>
+        <v>0.007235759921461332</v>
       </c>
       <c r="E40" t="n">
-        <v>0.007429655344243471</v>
+        <v>0.00736012737900222</v>
       </c>
       <c r="F40" t="n">
-        <v>0.007704098218114886</v>
+        <v>0.007653260197426806</v>
       </c>
       <c r="G40" t="n">
-        <v>0.007961232783697257</v>
+        <v>0.007924266235864856</v>
       </c>
     </row>
     <row r="41">
@@ -7360,19 +7361,19 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.007775577777744411</v>
+        <v>0.007687691909480824</v>
       </c>
       <c r="D41" t="n">
-        <v>0.007587312519594048</v>
+        <v>0.007503776138539844</v>
       </c>
       <c r="E41" t="n">
-        <v>0.007687363812272108</v>
+        <v>0.007618561930708134</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00794842909197537</v>
+        <v>0.007898117370800564</v>
       </c>
       <c r="G41" t="n">
-        <v>0.008193467087271452</v>
+        <v>0.008156874764324747</v>
       </c>
     </row>
     <row r="42">
@@ -7383,19 +7384,19 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.008049670625119132</v>
+        <v>0.007962080167079024</v>
       </c>
       <c r="D42" t="n">
-        <v>0.007853131827909624</v>
+        <v>0.007769877778378235</v>
       </c>
       <c r="E42" t="n">
-        <v>0.007943104952172795</v>
+        <v>0.007874532150568374</v>
       </c>
       <c r="F42" t="n">
-        <v>0.00818841481490791</v>
+        <v>0.008138266648310613</v>
       </c>
       <c r="G42" t="n">
-        <v>0.008420459496240193</v>
+        <v>0.008383979148403966</v>
       </c>
     </row>
     <row r="43">
@@ -7406,19 +7407,19 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.008309978844785335</v>
+        <v>0.008223476386409275</v>
       </c>
       <c r="D43" t="n">
-        <v>0.008103554246465309</v>
+        <v>0.008021334044425926</v>
       </c>
       <c r="E43" t="n">
-        <v>0.008182748052035792</v>
+        <v>0.008115023962472634</v>
       </c>
       <c r="F43" t="n">
-        <v>0.008416886666112738</v>
+        <v>0.008367357057276205</v>
       </c>
       <c r="G43" t="n">
-        <v>0.008634795270890019</v>
+        <v>0.00859875665452892</v>
       </c>
     </row>
     <row r="44">
@@ -7429,19 +7430,19 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.008579531944732811</v>
+        <v>0.008493657494282571</v>
       </c>
       <c r="D44" t="n">
-        <v>0.008361210107091708</v>
+        <v>0.008279587621811905</v>
       </c>
       <c r="E44" t="n">
-        <v>0.008428305480996903</v>
+        <v>0.008361067715587776</v>
       </c>
       <c r="F44" t="n">
-        <v>0.008647824569306545</v>
+        <v>0.008598648583236959</v>
       </c>
       <c r="G44" t="n">
-        <v>0.008849150685087501</v>
+        <v>0.008813361164428988</v>
       </c>
     </row>
     <row r="45">
@@ -7452,19 +7453,19 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.008857793650026646</v>
+        <v>0.008770960948703088</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00862697511426787</v>
+        <v>0.008544442641636129</v>
       </c>
       <c r="E45" t="n">
-        <v>0.008677541050088149</v>
+        <v>0.008609547180058331</v>
       </c>
       <c r="F45" t="n">
-        <v>0.008872642924834237</v>
+        <v>0.008822911116825698</v>
       </c>
       <c r="G45" t="n">
-        <v>0.009052967960907942</v>
+        <v>0.009016767376006773</v>
       </c>
     </row>
     <row r="46">
@@ -7475,19 +7476,19 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00912014945934402</v>
+        <v>0.009033752093691866</v>
       </c>
       <c r="D46" t="n">
-        <v>0.008877072923452045</v>
+        <v>0.008794956176575153</v>
       </c>
       <c r="E46" t="n">
-        <v>0.008910562705958695</v>
+        <v>0.00884290551374348</v>
       </c>
       <c r="F46" t="n">
-        <v>0.009080122410505436</v>
+        <v>0.009030632839905996</v>
       </c>
       <c r="G46" t="n">
-        <v>0.009239095009251273</v>
+        <v>0.009203065058671689</v>
       </c>
     </row>
     <row r="47">
@@ -7498,19 +7499,19 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.009370986626933472</v>
+        <v>0.009285126440025106</v>
       </c>
       <c r="D47" t="n">
-        <v>0.009113138683221538</v>
+        <v>0.009031531667414723</v>
       </c>
       <c r="E47" t="n">
-        <v>0.009126658089326939</v>
+        <v>0.009059414250391536</v>
       </c>
       <c r="F47" t="n">
-        <v>0.009270545185568434</v>
+        <v>0.009221355011549266</v>
       </c>
       <c r="G47" t="n">
-        <v>0.009407941516819559</v>
+        <v>0.009372123932450526</v>
       </c>
     </row>
     <row r="48">
@@ -7521,19 +7522,19 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.009617160587365985</v>
+        <v>0.00953103123135945</v>
       </c>
       <c r="D48" t="n">
-        <v>0.009339580091971004</v>
+        <v>0.009257715607995319</v>
       </c>
       <c r="E48" t="n">
-        <v>0.009331013077041227</v>
+        <v>0.009263551552293544</v>
       </c>
       <c r="F48" t="n">
-        <v>0.009445978210532027</v>
+        <v>0.009396626333895378</v>
       </c>
       <c r="G48" t="n">
-        <v>0.009563249864421156</v>
+        <v>0.009527312455565776</v>
       </c>
     </row>
     <row r="49">
@@ -7544,19 +7545,19 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.009840389486040567</v>
+        <v>0.009754579450795406</v>
       </c>
       <c r="D49" t="n">
-        <v>0.009540646916238977</v>
+        <v>0.009459084884108033</v>
       </c>
       <c r="E49" t="n">
-        <v>0.009507890389094251</v>
+        <v>0.009440674088833253</v>
       </c>
       <c r="F49" t="n">
-        <v>0.009596868901643893</v>
+        <v>0.00954769353449493</v>
       </c>
       <c r="G49" t="n">
-        <v>0.00969313946446638</v>
+        <v>0.009657327356534483</v>
       </c>
     </row>
     <row r="50">
@@ -7567,19 +7568,19 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.01004209355657543</v>
+        <v>0.009957634456221913</v>
       </c>
       <c r="D50" t="n">
-        <v>0.009713591109363897</v>
+        <v>0.009633310843003522</v>
       </c>
       <c r="E50" t="n">
-        <v>0.009655050114391717</v>
+        <v>0.0095888882047028</v>
       </c>
       <c r="F50" t="n">
-        <v>0.009720439418706456</v>
+        <v>0.009672033890958436</v>
       </c>
       <c r="G50" t="n">
-        <v>0.00979827229314343</v>
+        <v>0.009763017915905288</v>
       </c>
     </row>
     <row r="51">
@@ -7590,19 +7591,19 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.01021333982314471</v>
+        <v>0.01012989956293456</v>
       </c>
       <c r="D51" t="n">
-        <v>0.009854338916503488</v>
+        <v>0.009775027492134776</v>
       </c>
       <c r="E51" t="n">
-        <v>0.009773088396051743</v>
+        <v>0.009707725234451389</v>
       </c>
       <c r="F51" t="n">
-        <v>0.009814799000177017</v>
+        <v>0.009766974647295947</v>
       </c>
       <c r="G51" t="n">
-        <v>0.00987387089372522</v>
+        <v>0.009839036024706375</v>
       </c>
     </row>
     <row r="52">
@@ -7613,19 +7614,19 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.01033522857027094</v>
+        <v>0.01025300909558193</v>
       </c>
       <c r="D52" t="n">
-        <v>0.009939845624511653</v>
+        <v>0.009861698056112223</v>
       </c>
       <c r="E52" t="n">
-        <v>0.009841989582442374</v>
+        <v>0.009777583659852044</v>
       </c>
       <c r="F52" t="n">
-        <v>0.009868358208939191</v>
+        <v>0.009821231160565137</v>
       </c>
       <c r="G52" t="n">
-        <v>0.009910555731323331</v>
+        <v>0.009876220917556066</v>
       </c>
     </row>
     <row r="53">
@@ -7636,19 +7637,19 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.01039545371414145</v>
+        <v>0.01031434664620682</v>
       </c>
       <c r="D53" t="n">
-        <v>0.009960536776669804</v>
+        <v>0.009883455394266185</v>
       </c>
       <c r="E53" t="n">
-        <v>0.009855278488429417</v>
+        <v>0.009791754109742215</v>
       </c>
       <c r="F53" t="n">
-        <v>0.009884143298928585</v>
+        <v>0.009837652068754902</v>
       </c>
       <c r="G53" t="n">
-        <v>0.009903730619087493</v>
+        <v>0.009869853844410609</v>
       </c>
     </row>
     <row r="54">
@@ -7659,19 +7660,19 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.01043728709471286</v>
+        <v>0.01035554727327422</v>
       </c>
       <c r="D54" t="n">
-        <v>0.009987439732508376</v>
+        <v>0.009909758511076359</v>
       </c>
       <c r="E54" t="n">
-        <v>0.009882185193822775</v>
+        <v>0.009818168453312777</v>
       </c>
       <c r="F54" t="n">
-        <v>0.00991195075861314</v>
+        <v>0.009865092394976085</v>
       </c>
       <c r="G54" t="n">
-        <v>0.009918142328223488</v>
+        <v>0.009883996117768766</v>
       </c>
     </row>
     <row r="55">
@@ -7682,19 +7683,19 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.01048426530848716</v>
+        <v>0.01040405611639269</v>
       </c>
       <c r="D55" t="n">
-        <v>0.01003410316432812</v>
+        <v>0.009957877536856197</v>
       </c>
       <c r="E55" t="n">
-        <v>0.009931243155245051</v>
+        <v>0.009868424088264218</v>
       </c>
       <c r="F55" t="n">
-        <v>0.00996179667916618</v>
+        <v>0.009915812524857532</v>
       </c>
       <c r="G55" t="n">
-        <v>0.009956825728835559</v>
+        <v>0.00992331482554522</v>
       </c>
     </row>
     <row r="56">
@@ -7705,19 +7706,19 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.01054221666697014</v>
+        <v>0.01046252864760524</v>
       </c>
       <c r="D56" t="n">
-        <v>0.01010121617670372</v>
+        <v>0.01002548139151197</v>
       </c>
       <c r="E56" t="n">
-        <v>0.009999660596670273</v>
+        <v>0.009937245008163219</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01003179230090934</v>
+        <v>0.009986105209891103</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01002427484021084</v>
+        <v>0.009990980873607109</v>
       </c>
     </row>
     <row r="57">
@@ -7728,19 +7729,19 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.01063269553958926</v>
+        <v>0.01055286943997545</v>
       </c>
       <c r="D57" t="n">
-        <v>0.01020722743149638</v>
+        <v>0.01013135974859024</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01009977044129774</v>
+        <v>0.01003724299065234</v>
       </c>
       <c r="F57" t="n">
-        <v>0.01012635204452382</v>
+        <v>0.01008058855130087</v>
       </c>
       <c r="G57" t="n">
-        <v>0.01012067297246779</v>
+        <v>0.0100873255516223</v>
       </c>
     </row>
     <row r="58">
@@ -7751,19 +7752,19 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.01076503322541611</v>
+        <v>0.01068575714906135</v>
       </c>
       <c r="D58" t="n">
-        <v>0.01035130678370127</v>
+        <v>0.01027596207167417</v>
       </c>
       <c r="E58" t="n">
-        <v>0.01022823867149232</v>
+        <v>0.01016614141265187</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01023980102491686</v>
+        <v>0.01019436260040958</v>
       </c>
       <c r="G58" t="n">
-        <v>0.01023905230646596</v>
+        <v>0.01020594642977923</v>
       </c>
     </row>
     <row r="59">
@@ -8122,7 +8123,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
+      <c r="A3" s="2" t="n"/>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
@@ -8166,7 +8167,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
@@ -8210,7 +8211,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
@@ -8254,7 +8255,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n"/>
+      <c r="A9" s="2" t="n"/>
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
@@ -8298,7 +8299,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="2" t="n"/>
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
@@ -8342,7 +8343,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
+      <c r="A13" s="2" t="n"/>
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
@@ -8386,7 +8387,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n"/>
+      <c r="A15" s="2" t="n"/>
       <c r="B15" s="1" t="n">
         <v>1</v>
       </c>
@@ -8430,7 +8431,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n"/>
+      <c r="A17" s="2" t="n"/>
       <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
@@ -8474,7 +8475,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n"/>
+      <c r="A19" s="2" t="n"/>
       <c r="B19" s="1" t="n">
         <v>1</v>
       </c>
@@ -8518,7 +8519,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n"/>
+      <c r="A21" s="2" t="n"/>
       <c r="B21" s="1" t="n">
         <v>1</v>
       </c>
@@ -8562,7 +8563,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n"/>
+      <c r="A23" s="2" t="n"/>
       <c r="B23" s="1" t="n">
         <v>1</v>
       </c>
@@ -8606,7 +8607,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n"/>
+      <c r="A25" s="2" t="n"/>
       <c r="B25" s="1" t="n">
         <v>1</v>
       </c>
@@ -8650,7 +8651,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n"/>
+      <c r="A27" s="2" t="n"/>
       <c r="B27" s="1" t="n">
         <v>1</v>
       </c>
@@ -8694,7 +8695,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n"/>
+      <c r="A29" s="2" t="n"/>
       <c r="B29" s="1" t="n">
         <v>1</v>
       </c>
@@ -8738,7 +8739,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n"/>
+      <c r="A31" s="2" t="n"/>
       <c r="B31" s="1" t="n">
         <v>1</v>
       </c>
@@ -8782,7 +8783,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n"/>
+      <c r="A33" s="2" t="n"/>
       <c r="B33" s="1" t="n">
         <v>1</v>
       </c>
@@ -8826,7 +8827,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n"/>
+      <c r="A35" s="2" t="n"/>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
@@ -8870,7 +8871,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n"/>
+      <c r="A37" s="2" t="n"/>
       <c r="B37" s="1" t="n">
         <v>1</v>
       </c>
@@ -8914,7 +8915,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n"/>
+      <c r="A39" s="2" t="n"/>
       <c r="B39" s="1" t="n">
         <v>1</v>
       </c>
@@ -8958,7 +8959,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n"/>
+      <c r="A41" s="2" t="n"/>
       <c r="B41" s="1" t="n">
         <v>1</v>
       </c>
@@ -9002,7 +9003,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n"/>
+      <c r="A43" s="2" t="n"/>
       <c r="B43" s="1" t="n">
         <v>1</v>
       </c>
@@ -9046,7 +9047,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n"/>
+      <c r="A45" s="2" t="n"/>
       <c r="B45" s="1" t="n">
         <v>1</v>
       </c>
@@ -9090,7 +9091,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n"/>
+      <c r="A47" s="2" t="n"/>
       <c r="B47" s="1" t="n">
         <v>1</v>
       </c>
@@ -9134,7 +9135,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n"/>
+      <c r="A49" s="2" t="n"/>
       <c r="B49" s="1" t="n">
         <v>1</v>
       </c>
@@ -9178,7 +9179,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n"/>
+      <c r="A51" s="2" t="n"/>
       <c r="B51" s="1" t="n">
         <v>1</v>
       </c>
@@ -9222,7 +9223,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n"/>
+      <c r="A53" s="2" t="n"/>
       <c r="B53" s="1" t="n">
         <v>1</v>
       </c>
@@ -9266,7 +9267,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n"/>
+      <c r="A55" s="2" t="n"/>
       <c r="B55" s="1" t="n">
         <v>1</v>
       </c>
@@ -9310,7 +9311,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n"/>
+      <c r="A57" s="2" t="n"/>
       <c r="B57" s="1" t="n">
         <v>1</v>
       </c>
@@ -9354,7 +9355,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n"/>
+      <c r="A59" s="2" t="n"/>
       <c r="B59" s="1" t="n">
         <v>1</v>
       </c>
@@ -9398,7 +9399,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n"/>
+      <c r="A61" s="2" t="n"/>
       <c r="B61" s="1" t="n">
         <v>1</v>
       </c>
@@ -9442,7 +9443,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n"/>
+      <c r="A63" s="2" t="n"/>
       <c r="B63" s="1" t="n">
         <v>1</v>
       </c>
@@ -9486,7 +9487,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n"/>
+      <c r="A65" s="2" t="n"/>
       <c r="B65" s="1" t="n">
         <v>1</v>
       </c>
@@ -9530,7 +9531,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n"/>
+      <c r="A67" s="2" t="n"/>
       <c r="B67" s="1" t="n">
         <v>1</v>
       </c>
@@ -9574,7 +9575,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n"/>
+      <c r="A69" s="2" t="n"/>
       <c r="B69" s="1" t="n">
         <v>1</v>
       </c>
@@ -9618,7 +9619,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n"/>
+      <c r="A71" s="2" t="n"/>
       <c r="B71" s="1" t="n">
         <v>1</v>
       </c>
@@ -9662,7 +9663,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n"/>
+      <c r="A73" s="2" t="n"/>
       <c r="B73" s="1" t="n">
         <v>1</v>
       </c>
@@ -9706,7 +9707,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n"/>
+      <c r="A75" s="2" t="n"/>
       <c r="B75" s="1" t="n">
         <v>1</v>
       </c>
@@ -9750,7 +9751,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n"/>
+      <c r="A77" s="2" t="n"/>
       <c r="B77" s="1" t="n">
         <v>1</v>
       </c>
@@ -9794,7 +9795,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n"/>
+      <c r="A79" s="2" t="n"/>
       <c r="B79" s="1" t="n">
         <v>1</v>
       </c>
@@ -9838,7 +9839,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n"/>
+      <c r="A81" s="2" t="n"/>
       <c r="B81" s="1" t="n">
         <v>1</v>
       </c>
@@ -9882,7 +9883,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n"/>
+      <c r="A83" s="2" t="n"/>
       <c r="B83" s="1" t="n">
         <v>1</v>
       </c>
@@ -9926,7 +9927,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n"/>
+      <c r="A85" s="2" t="n"/>
       <c r="B85" s="1" t="n">
         <v>1</v>
       </c>
@@ -9970,7 +9971,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n"/>
+      <c r="A87" s="2" t="n"/>
       <c r="B87" s="1" t="n">
         <v>1</v>
       </c>
@@ -10014,7 +10015,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n"/>
+      <c r="A89" s="2" t="n"/>
       <c r="B89" s="1" t="n">
         <v>1</v>
       </c>
@@ -10058,7 +10059,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n"/>
+      <c r="A91" s="2" t="n"/>
       <c r="B91" s="1" t="n">
         <v>1</v>
       </c>
@@ -10102,7 +10103,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n"/>
+      <c r="A93" s="2" t="n"/>
       <c r="B93" s="1" t="n">
         <v>1</v>
       </c>
@@ -10146,7 +10147,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n"/>
+      <c r="A95" s="2" t="n"/>
       <c r="B95" s="1" t="n">
         <v>1</v>
       </c>
@@ -10190,7 +10191,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n"/>
+      <c r="A97" s="2" t="n"/>
       <c r="B97" s="1" t="n">
         <v>1</v>
       </c>
@@ -10234,7 +10235,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n"/>
+      <c r="A99" s="2" t="n"/>
       <c r="B99" s="1" t="n">
         <v>1</v>
       </c>
@@ -10278,7 +10279,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n"/>
+      <c r="A101" s="2" t="n"/>
       <c r="B101" s="1" t="n">
         <v>1</v>
       </c>
@@ -10322,7 +10323,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n"/>
+      <c r="A103" s="2" t="n"/>
       <c r="B103" s="1" t="n">
         <v>1</v>
       </c>
@@ -10366,15 +10367,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n"/>
+      <c r="A105" s="2" t="n"/>
       <c r="B105" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -10400,15 +10396,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n"/>
+      <c r="A107" s="2" t="n"/>
       <c r="B107" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -10434,15 +10425,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n"/>
+      <c r="A109" s="2" t="n"/>
       <c r="B109" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -10468,15 +10454,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n"/>
+      <c r="A111" s="2" t="n"/>
       <c r="B111" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -10502,15 +10483,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n"/>
+      <c r="A113" s="2" t="n"/>
       <c r="B113" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -10536,15 +10512,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n"/>
+      <c r="A115" s="2" t="n"/>
       <c r="B115" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -10570,7 +10541,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n"/>
+      <c r="A117" s="2" t="n"/>
       <c r="B117" s="1" t="n">
         <v>1</v>
       </c>
